--- a/analysis/aggregate/at-PRF.xlsx
+++ b/analysis/aggregate/at-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,22 +518,22 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.795621265304199</v>
+        <v>0.7889029306185165</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02825836061055326</v>
+        <v>0.01068169063123899</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7905882352941177</v>
+        <v>0.7823529411764706</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01933138438253525</v>
+        <v>0.01100487466698219</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7930225248217134</v>
+        <v>0.7855852007934682</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02260645453306452</v>
+        <v>0.009464712501638529</v>
       </c>
     </row>
     <row r="3">
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -571,22 +571,22 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.795621265304199</v>
+        <v>0.74416576738392</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02825836061055326</v>
+        <v>0.008406021695543766</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7905882352941177</v>
+        <v>0.7458823529411764</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01933138438253525</v>
+        <v>0.00644379479417841</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7930225248217134</v>
+        <v>0.7450137901089717</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02260645453306452</v>
+        <v>0.006884466410366893</v>
       </c>
     </row>
     <row r="4">
@@ -597,7 +597,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -624,22 +624,22 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7907973978020022</v>
+        <v>0.7834538312366367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009486131970237538</v>
+        <v>0.01805710411629546</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7870588235294118</v>
+        <v>0.7788235294117647</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01735044847500309</v>
+        <v>0.01744987879316632</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7888611177812913</v>
+        <v>0.7811263651923566</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01159848018970388</v>
+        <v>0.01760418156681617</v>
       </c>
     </row>
     <row r="5">
@@ -650,7 +650,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -677,22 +677,22 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7907973978020022</v>
+        <v>0.7399093205540419</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009486131970237538</v>
+        <v>0.02148221049073106</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7870588235294118</v>
+        <v>0.7458823529411764</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01735044847500309</v>
+        <v>0.01735044847500311</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7888611177812913</v>
+        <v>0.7428668729475068</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01159848018970388</v>
+        <v>0.01912206584819848</v>
       </c>
     </row>
     <row r="6">
@@ -703,7 +703,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -727,25 +727,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8070779587497745</v>
+        <v>0.8215195316849346</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01114265520412314</v>
+        <v>0.012265197677139</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7942857142857143</v>
+        <v>0.7988571428571428</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00808122035641768</v>
+        <v>0.007450517034517328</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8005881746321406</v>
+        <v>0.8099863470812823</v>
       </c>
       <c r="M6" t="n">
-        <v>0.006931284626390157</v>
+        <v>0.007536368183006271</v>
       </c>
     </row>
     <row r="7">
@@ -756,7 +756,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -783,22 +783,22 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8092987306361833</v>
+        <v>0.8215195316849346</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01085256709750265</v>
+        <v>0.012265197677139</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.7988571428571428</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01456862718169365</v>
+        <v>0.007450517034517328</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8045731038082765</v>
+        <v>0.8099863470812823</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01074385092148641</v>
+        <v>0.007536368183006271</v>
       </c>
     </row>
     <row r="8">
@@ -809,7 +809,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -836,22 +836,22 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8439532366857948</v>
+        <v>0.8051818056177755</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02286373852618294</v>
+        <v>0.0190651965632851</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8217142857142857</v>
+        <v>0.8148571428571429</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02599843009389101</v>
+        <v>0.008666143364630353</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8326134694657897</v>
+        <v>0.809841030716383</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02300642970598781</v>
+        <v>0.008387350806835801</v>
       </c>
     </row>
     <row r="9">
@@ -862,48 +862,472 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8051818056177755</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0190651965632851</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8148571428571429</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.008666143364630353</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.809841030716383</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.008387350806835801</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>t5-base</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.795621265304199</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.02825836061055326</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7905882352941177</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01933138438253525</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7930225248217134</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.02260645453306452</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.795621265304199</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.02825836061055326</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7905882352941177</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01933138438253525</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7930225248217134</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.02260645453306452</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7907973978020022</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.009486131970237538</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7870588235294118</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.01735044847500309</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7888611177812913</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.01159848018970388</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7907973978020022</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.009486131970237538</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7870588235294118</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.01735044847500309</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7888611177812913</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01159848018970388</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>paraphrase</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8070779587497745</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.01114265520412314</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.00808122035641768</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.8005881746321406</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.006931284626390157</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8092987306361833</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.01085256709750265</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.01456862718169365</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.8045731038082765</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.01074385092148641</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.8439532366857948</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I16" t="n">
         <v>0.02286373852618294</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J16" t="n">
         <v>0.8217142857142857</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K16" t="n">
         <v>0.02599843009389101</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L16" t="n">
         <v>0.8326134694657897</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M16" t="n">
+        <v>0.02300642970598781</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8439532366857948</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.02286373852618294</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.8217142857142857</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.02599843009389101</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8326134694657897</v>
+      </c>
+      <c r="M17" t="n">
         <v>0.02300642970598781</v>
       </c>
     </row>

--- a/analysis/aggregate/at-PRF.xlsx
+++ b/analysis/aggregate/at-PRF.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -518,22 +518,22 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7889029306185165</v>
+        <v>0.8032257372799156</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01068169063123899</v>
+        <v>0.0232035910679388</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7823529411764706</v>
+        <v>0.7952941176470588</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01100487466698219</v>
+        <v>0.01131493180098317</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7855852007934682</v>
+        <v>0.7991525361753453</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009464712501638529</v>
+        <v>0.01548799997339644</v>
       </c>
     </row>
     <row r="3">
@@ -554,39 +554,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.74416576738392</v>
+        <v>0.7964932045147748</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008406021695543766</v>
+        <v>0.02616269895879725</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7458823529411764</v>
+        <v>0.7905882352941177</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00644379479417841</v>
+        <v>0.01977380742820191</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7450137901089717</v>
+        <v>0.7934547305069315</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006884466410366893</v>
+        <v>0.02136648410049956</v>
       </c>
     </row>
     <row r="4">
@@ -612,7 +612,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,22 +624,22 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7834538312366367</v>
+        <v>0.791556177627514</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01805710411629546</v>
+        <v>0.03293894958061917</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7788235294117647</v>
+        <v>0.7835294117647058</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01744987879316632</v>
+        <v>0.01632286697119014</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7811263651923566</v>
+        <v>0.7874416448914973</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01760418156681617</v>
+        <v>0.02435085399303715</v>
       </c>
     </row>
     <row r="5">
@@ -670,29 +670,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7399093205540419</v>
+        <v>0.7810757487658332</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02148221049073106</v>
+        <v>0.02097093959356394</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7458823529411764</v>
+        <v>0.78</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01735044847500311</v>
+        <v>0.01476458870354255</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7428668729475068</v>
+        <v>0.7805181332701095</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01912206584819848</v>
+        <v>0.01763698554161779</v>
       </c>
     </row>
     <row r="6">
@@ -730,22 +730,22 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8215195316849346</v>
+        <v>0.8146069153948829</v>
       </c>
       <c r="I6" t="n">
-        <v>0.012265197677139</v>
+        <v>0.0120152097919216</v>
       </c>
       <c r="J6" t="n">
         <v>0.7988571428571428</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007450517034517328</v>
+        <v>0.0240407816776716</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8099863470812823</v>
+        <v>0.8065822771029861</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007536368183006271</v>
+        <v>0.01723660889004978</v>
       </c>
     </row>
     <row r="7">
@@ -771,34 +771,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8215195316849346</v>
+        <v>0.8260473064144481</v>
       </c>
       <c r="I7" t="n">
-        <v>0.012265197677139</v>
+        <v>0.01053222150680252</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7988571428571428</v>
+        <v>0.8034285714285716</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007450517034517328</v>
+        <v>0.01490103406903462</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8099863470812823</v>
+        <v>0.814571339579258</v>
       </c>
       <c r="M7" t="n">
-        <v>0.007536368183006271</v>
+        <v>0.01260387585542907</v>
       </c>
     </row>
     <row r="8">
@@ -819,12 +819,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -836,22 +836,22 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8051818056177755</v>
+        <v>0.8139826225733712</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0190651965632851</v>
+        <v>0.008880027578887032</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8148571428571429</v>
+        <v>0.7954285714285715</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008666143364630353</v>
+        <v>0.01585649934344181</v>
       </c>
       <c r="L8" t="n">
-        <v>0.809841030716383</v>
+        <v>0.8045794310407089</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008387350806835801</v>
+        <v>0.01222398415351354</v>
       </c>
     </row>
     <row r="9">
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -882,29 +882,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8051818056177755</v>
+        <v>0.8210205572564359</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0190651965632851</v>
+        <v>0.02501929576776974</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8148571428571429</v>
+        <v>0.8057142857142857</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008666143364630353</v>
+        <v>0.01714285714285713</v>
       </c>
       <c r="L9" t="n">
-        <v>0.809841030716383</v>
+        <v>0.8132211442801068</v>
       </c>
       <c r="M9" t="n">
-        <v>0.008387350806835801</v>
+        <v>0.0194096155329323</v>
       </c>
     </row>
     <row r="10">
@@ -925,7 +925,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -942,22 +942,22 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.795621265304199</v>
+        <v>0.7819025169391415</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02825836061055326</v>
+        <v>0.03381961108117848</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7905882352941177</v>
+        <v>0.7741176470588236</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01933138438253525</v>
+        <v>0.009843059135695012</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7930225248217134</v>
+        <v>0.7775602986868405</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02260645453306452</v>
+        <v>0.01325441678112865</v>
       </c>
     </row>
     <row r="11">
@@ -978,39 +978,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.795621265304199</v>
+        <v>0.7693475123075588</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02825836061055326</v>
+        <v>0.02505037573582037</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7905882352941177</v>
+        <v>0.7752941176470588</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01933138438253525</v>
+        <v>0.01924167909858369</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7930225248217134</v>
+        <v>0.7721806007488473</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02260645453306452</v>
+        <v>0.01923478321792587</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1048,22 +1048,22 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7907973978020022</v>
+        <v>0.7910581412042036</v>
       </c>
       <c r="I12" t="n">
-        <v>0.009486131970237538</v>
+        <v>0.0162466219794255</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7870588235294118</v>
+        <v>0.7835294117647058</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01735044847500309</v>
+        <v>0.01275263728745814</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7888611177812913</v>
+        <v>0.7872572329790611</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01159848018970388</v>
+        <v>0.01392318661109562</v>
       </c>
     </row>
     <row r="13">
@@ -1094,29 +1094,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7907973978020022</v>
+        <v>0.7837077386465993</v>
       </c>
       <c r="I13" t="n">
-        <v>0.009486131970237538</v>
+        <v>0.01444665562511347</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7870588235294118</v>
+        <v>0.7882352941176471</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01735044847500309</v>
+        <v>0.01100487466698218</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7888611177812913</v>
+        <v>0.7859462192934539</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01159848018970388</v>
+        <v>0.01210540725637605</v>
       </c>
     </row>
     <row r="14">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1151,25 +1151,25 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8070779587497745</v>
+        <v>0.828668375476596</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01114265520412314</v>
+        <v>0.01386687459166112</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7942857142857143</v>
+        <v>0.8182857142857143</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00808122035641768</v>
+        <v>0.01685472137571735</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8005881746321406</v>
+        <v>0.8234377709864779</v>
       </c>
       <c r="M14" t="n">
-        <v>0.006931284626390157</v>
+        <v>0.01525316664838926</v>
       </c>
     </row>
     <row r="15">
@@ -1190,39 +1190,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8092987306361833</v>
+        <v>0.8307952915789528</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01085256709750265</v>
+        <v>0.02251057099690375</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8</v>
+        <v>0.8251428571428571</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01456862718169365</v>
+        <v>0.02510386587027289</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8045731038082765</v>
+        <v>0.8279501124088933</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01074385092148641</v>
+        <v>0.02365477038578901</v>
       </c>
     </row>
     <row r="16">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1260,22 +1260,22 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8439532366857948</v>
+        <v>0.8288818509733631</v>
       </c>
       <c r="I16" t="n">
-        <v>0.02286373852618294</v>
+        <v>0.008051117629415688</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8217142857142857</v>
+        <v>0.8022857142857143</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02599843009389101</v>
+        <v>0.02198329607048151</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8326134694657897</v>
+        <v>0.8152239007271126</v>
       </c>
       <c r="M16" t="n">
-        <v>0.02300642970598781</v>
+        <v>0.01169507659605252</v>
       </c>
     </row>
     <row r="17">
@@ -1306,29 +1306,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8439532366857948</v>
+        <v>0.8361303648526736</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02286373852618294</v>
+        <v>0.005129295819789958</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8217142857142857</v>
+        <v>0.8102857142857143</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02599843009389101</v>
+        <v>0.01685472137571733</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8326134694657897</v>
+        <v>0.8229171743555115</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02300642970598781</v>
+        <v>0.008526021348208714</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/aggregate/at-PRF.xlsx
+++ b/analysis/aggregate/at-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,32 +454,92 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>precision_mean</t>
+          <t>micro_precision_mean</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>precision_std</t>
+          <t>micro_precision_std</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>recall_mean</t>
+          <t>micro_recall_mean</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>recall_std</t>
+          <t>micro_recall_std</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>f1_mean</t>
+          <t>micro_f1_mean</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>f1_std</t>
+          <t>micro_f1_std</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>macro_precision_mean</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>macro_precision_std</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>macro_recall_mean</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>macro_recall_std</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>macro_f1_mean</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>macro_f1_std</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>weighted_precision_mean</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>weighted_precision_std</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>weighted_recall_mean</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>weighted_recall_std</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>weighted_f1_mean</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>weighted_f1_std</t>
         </is>
       </c>
     </row>
@@ -518,22 +578,58 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8032257372799156</v>
+        <v>0.8445420321789637</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0232035910679388</v>
+        <v>0.01331521361306525</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7952941176470588</v>
+        <v>0.8364705882352942</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01131493180098317</v>
+        <v>0.01735044847500312</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7991525361753453</v>
+        <v>0.8403950589244706</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01548799997339644</v>
+        <v>0.0119056580090543</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.8581267217630855</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01266169167413938</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.8553719008264462</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.01505730792636052</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.8496969696969698</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.01245410641816642</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.8560784313725491</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.01107886516589545</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8364705882352942</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.01735044847500312</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.8375294117647056</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.01212963427650069</v>
       </c>
     </row>
     <row r="3">
@@ -571,22 +667,58 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7964932045147748</v>
+        <v>0.8415711953410463</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02616269895879725</v>
+        <v>0.02091289578060903</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7905882352941177</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01977380742820191</v>
+        <v>0.007204381596421133</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7934547305069315</v>
+        <v>0.8383435801237681</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02136648410049956</v>
+        <v>0.01272080100535043</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8495867768595042</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01525758017195371</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8426997245179064</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.008229955507597534</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.8398347107438017</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.01104954522438384</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.8586274509803923</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.01680164489118833</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.007204381596421133</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.8389803921568625</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.01102442152904098</v>
       </c>
     </row>
     <row r="4">
@@ -624,22 +756,58 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.791556177627514</v>
+        <v>0.8304723810758763</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03293894958061917</v>
+        <v>0.01784655638454192</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7835294117647058</v>
+        <v>0.8223529411764705</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01632286697119014</v>
+        <v>0.00644379479417846</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7874416448914973</v>
+        <v>0.826307345133495</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02435085399303715</v>
+        <v>0.00953515652688987</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.8396694214876034</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01283285366264697</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.8382920110192836</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.008066969952807866</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.8317355371900828</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.009255132432395227</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.8405882352941176</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.01303589814791736</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8223529411764705</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.00644379479417846</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.8225490196078431</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.006806492140278298</v>
       </c>
     </row>
     <row r="5">
@@ -677,22 +845,58 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7810757487658332</v>
+        <v>0.8339616132392006</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02097093959356394</v>
+        <v>0.007487007915949849</v>
       </c>
       <c r="J5" t="n">
-        <v>0.78</v>
+        <v>0.8329411764705883</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01476458870354255</v>
+        <v>0.007892004626469858</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7805181332701095</v>
+        <v>0.8334299195482171</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01763698554161779</v>
+        <v>0.006096166136270602</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8349862258953168</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.006845605311178604</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.8363636363636363</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.00718369411041615</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.828374655647383</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.006750716669334903</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8470588235294118</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.005046877520091605</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8329411764705883</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.007892004626469858</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.8314509803921567</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.006007812419928562</v>
       </c>
     </row>
     <row r="6">
@@ -730,22 +934,58 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8146069153948829</v>
+        <v>0.8286896703481121</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0120152097919216</v>
+        <v>0.006291147208316797</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7988571428571428</v>
+        <v>0.8125714285714286</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0240407816776716</v>
+        <v>0.0173322867292607</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8065822771029861</v>
+        <v>0.8204767486050736</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01723660889004978</v>
+        <v>0.00994174494368151</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.8307162534435262</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.009510617821462277</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.8234159779614327</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.01696509006909326</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.819456906729634</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.01392711994935038</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.8399047619047619</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.006436503043467873</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8125714285714286</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.0173322867292607</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.8165496598639456</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.01177045168153138</v>
       </c>
     </row>
     <row r="7">
@@ -783,22 +1023,58 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8260473064144481</v>
+        <v>0.8436950951729664</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01053222150680252</v>
+        <v>0.007065861311344474</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8034285714285716</v>
+        <v>0.8205714285714286</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01490103406903462</v>
+        <v>0.0111391935369245</v>
       </c>
       <c r="L7" t="n">
-        <v>0.814571339579258</v>
+        <v>0.8319628189293524</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01260387585542907</v>
+        <v>0.008843825959163974</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8358126721763085</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.005213275721150277</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.8225895316804408</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.009612312023343146</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.8217866981503346</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.007017243613423065</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.8573333333333334</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.007518684209680443</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.8205714285714286</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.0111391935369245</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.8290013605442177</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.008696366202950596</v>
       </c>
     </row>
     <row r="8">
@@ -836,22 +1112,58 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8139826225733712</v>
+        <v>0.8291607440881184</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008880027578887032</v>
+        <v>0.01193755855935166</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7954285714285715</v>
+        <v>0.8102857142857143</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01585649934344181</v>
+        <v>0.01912365774935026</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8045794310407089</v>
+        <v>0.8195951611790561</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01222398415351354</v>
+        <v>0.01546727986438244</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8273002754820936</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.008585036028618959</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.8228650137741049</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.0119921756802638</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.8176111767020858</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.01048439672903384</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.835104761904762</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.01370148211854825</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.8102857142857143</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.01912365774935026</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.8131020408163264</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.01734448962302482</v>
       </c>
     </row>
     <row r="9">
@@ -889,22 +1201,58 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8210205572564359</v>
+        <v>0.8384342707877479</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02501929576776974</v>
+        <v>0.02206435631602798</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.8228571428571427</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01714285714285713</v>
+        <v>0.01616244071283536</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8132211442801068</v>
+        <v>0.8304969735217487</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0194096155329323</v>
+        <v>0.017017143014453</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8359504132231406</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01939044663953059</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.8292011019283748</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0150573079263605</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.8239748130657223</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.01715973625048729</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.8553333333333335</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.01706131399904915</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.8228571428571427</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.01616244071283536</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.828282993197279</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.01636346841928284</v>
       </c>
     </row>
     <row r="10">
@@ -942,22 +1290,58 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7819025169391415</v>
+        <v>0.8253637835048286</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03381961108117848</v>
+        <v>0.02303198995456285</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7741176470588236</v>
+        <v>0.8176470588235294</v>
       </c>
       <c r="K10" t="n">
-        <v>0.009843059135695012</v>
+        <v>0.02037706832433972</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7775602986868405</v>
+        <v>0.8210393010109017</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01325441678112865</v>
+        <v>0.003408516479051532</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.8347107438016529</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.009980287015281969</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.8319559228650139</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.01434756656749294</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.8267768595041323</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.004045930772218267</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.8366666666666667</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.007738269513988589</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.8176470588235294</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.02037706832433972</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.819019607843137</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.008204892530551979</v>
       </c>
     </row>
     <row r="11">
@@ -995,22 +1379,58 @@
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7693475123075588</v>
+        <v>0.8182626068114093</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02505037573582037</v>
+        <v>0.01359946891761821</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7752941176470588</v>
+        <v>0.8247058823529413</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01924167909858369</v>
+        <v>0.01131493180098316</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7721806007488473</v>
+        <v>0.8213366913281007</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01923478321792587</v>
+        <v>0.004221748941915416</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.8230027548209368</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.007972339464731523</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.8209366391184574</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.007852447831261353</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8163478945297127</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.004467100766539025</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.8387254901960786</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.006161669161753197</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.8247058823529413</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.01131493180098316</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.8247507002801118</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.003527721795391521</v>
       </c>
     </row>
     <row r="12">
@@ -1048,22 +1468,58 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7910581412042036</v>
+        <v>0.8326506026607519</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0162466219794255</v>
+        <v>0.01440233857722244</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7835294117647058</v>
+        <v>0.8247058823529411</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01275263728745814</v>
+        <v>0.007669649888473737</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7872572329790611</v>
+        <v>0.828639757785943</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01392318661109562</v>
+        <v>0.01056660943490677</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.8413223140495869</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.00878740380591545</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.8336088154269973</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.006705598592087097</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.8315151515151514</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.00819206118805365</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.8464705882352943</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.008675224237501531</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.8247058823529411</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.007669649888473737</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.8274901960784311</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.008990147967455274</v>
       </c>
     </row>
     <row r="13">
@@ -1101,22 +1557,58 @@
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7837077386465993</v>
+        <v>0.8258376957673178</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01444665562511347</v>
+        <v>0.01839152784092408</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7882352941176471</v>
+        <v>0.8305882352941175</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01100487466698218</v>
+        <v>0.01404392516036863</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7859462192934539</v>
+        <v>0.8281863341231646</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01210540725637605</v>
+        <v>0.01572859363276349</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8253443526170801</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01519527864520293</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.8264462809917357</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.01243489675293931</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.8194490358126721</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.01429271616808008</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.841372549019608</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.01395811276487408</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.8305882352941175</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.01404392516036863</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.8280784313725489</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.01392736692286355</v>
       </c>
     </row>
     <row r="14">
@@ -1154,22 +1646,58 @@
         <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.828668375476596</v>
+        <v>0.8356251901429875</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01386687459166112</v>
+        <v>0.01235254600877185</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8182857142857143</v>
+        <v>0.8251428571428573</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01685472137571735</v>
+        <v>0.01490103406903464</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8234377709864779</v>
+        <v>0.8303443173820282</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01525316664838926</v>
+        <v>0.01346723441859725</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.8424242424242424</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.009560359885748765</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.8371900826446282</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.009000721351352362</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.8329161747343565</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.01063501133082429</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.8478095238095238</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.01135192552617954</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.8251428571428573</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.01490103406903464</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.8278585034013606</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.01528898693127209</v>
       </c>
     </row>
     <row r="15">
@@ -1207,22 +1735,58 @@
         <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8307952915789528</v>
+        <v>0.8400175006307459</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02251057099690375</v>
+        <v>0.01523572109580819</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8251428571428571</v>
+        <v>0.8342857142857143</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02510386587027289</v>
+        <v>0.01807015805810501</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8279501124088933</v>
+        <v>0.8371323975640598</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02365477038578901</v>
+        <v>0.01643554240107812</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8342975206611571</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.01934268835431622</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.8300275482093665</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.01862307854672788</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.8262022825659189</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.01937757574120524</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.8522857142857143</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.01715079181448912</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.8342857142857143</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.01807015805810501</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.8361795918367345</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.01813149250360174</v>
       </c>
     </row>
     <row r="16">
@@ -1260,22 +1824,58 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8288818509733631</v>
+        <v>0.8359796432630692</v>
       </c>
       <c r="I16" t="n">
-        <v>0.008051117629415688</v>
+        <v>0.007140353443856621</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8022857142857143</v>
+        <v>0.8091428571428571</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02198329607048151</v>
+        <v>0.02122762928115057</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8152239007271126</v>
+        <v>0.8221982688197036</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01169507659605252</v>
+        <v>0.01055068071639365</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8359504132231406</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.005729100369995984</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.8247933884297522</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.008947868743202053</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.8243919716646989</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.003972805864748158</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.838952380952381</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.006854496843979633</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.8091428571428571</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.02122762928115057</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.8159673469387755</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.01370881005037859</v>
       </c>
     </row>
     <row r="17">
@@ -1313,22 +1913,58 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8361303648526736</v>
+        <v>0.8516212510208877</v>
       </c>
       <c r="I17" t="n">
-        <v>0.005129295819789958</v>
+        <v>0.0121518936365481</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8102857142857143</v>
+        <v>0.8251428571428571</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01685472137571733</v>
+        <v>0.009561828874675181</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8229171743555115</v>
+        <v>0.8380827151312822</v>
       </c>
       <c r="M17" t="n">
-        <v>0.008526021348208714</v>
+        <v>0.004866896365474133</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8400826446280991</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.008634946566753406</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.8247933884297522</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.007816121740557076</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.8266509248327431</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.005776979598846005</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.8595238095238095</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.009677334015667444</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.8251428571428571</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.009561828874675181</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.834938775510204</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.004975054622273895</v>
       </c>
     </row>
   </sheetData>
